--- a/backend/data/attachments/trust_contract_3.xlsx
+++ b/backend/data/attachments/trust_contract_3.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20463</v>
+        <v>46198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -464,7 +464,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2024-05-30</t>
         </is>
       </c>
     </row>
@@ -475,11 +475,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1629</v>
+        <v>314</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -489,7 +489,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2024-05-30</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>121</v>
+        <v>221</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2024-05-30</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2024-05-30</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>210</v>
+        <v>459</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2024-05-30</t>
         </is>
       </c>
     </row>
